--- a/config/excel/stages.xlsx
+++ b/config/excel/stages.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,11 @@
           <t>boss_id</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>display_name_en</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -544,13 +549,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>第1关</t>
+          <t>第1关·出击</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -580,6 +585,11 @@
         <v>0</v>
       </c>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Stage 1·Sortie</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -593,13 +603,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>第2关</t>
+          <t>第2关·冲锋潮</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -608,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -629,6 +639,11 @@
         <v>0</v>
       </c>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Stage 2·Charge</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -642,13 +657,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>第3关</t>
+          <t>第3关·长弓</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -663,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -678,6 +693,11 @@
         <v>0</v>
       </c>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Stage 3·Longbow</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -691,7 +711,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>第4关</t>
+          <t>第4关·铁盾试练</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -700,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -712,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -727,34 +747,31 @@
         <v>0</v>
       </c>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Stage 4·Shield Trial</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>第5关</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>wheel</t>
-        </is>
-      </c>
+          <t>第5关·分裂噩梦</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -766,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -784,29 +801,34 @@
         <v>0</v>
       </c>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Stage 5·Splinter</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>第6关</t>
+          <t>第6关·霰弹阵</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -818,13 +840,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -833,29 +855,34 @@
         <v>0</v>
       </c>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Stage 6·Buckshot</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>第7关</t>
+          <t>第7关·反弹陷阱</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -867,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -879,29 +906,34 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Stage 7·Ricochet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>第8关</t>
+          <t>第8关·十字锁</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -916,47 +948,52 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Stage 8·Cross Lock</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>第9关</t>
+          <t>第9关·火焰宗师</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -965,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -980,23 +1017,32 @@
         <v>0</v>
       </c>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Stage 9·Pyromaster</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>第10关</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>第10关·打造</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>attr_forge</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>0</v>
@@ -1028,9 +1074,10 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>lancer_knight</t>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Stage 10·Forge</t>
         </is>
       </c>
     </row>
@@ -1039,75 +1086,80 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>第11关</t>
+          <t>第11关·硬拆快攻</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Stage 11·Bash &amp; Break</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>第12关</t>
+          <t>第12关·弹幕包围</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1116,145 +1168,152 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Stage 12·Barrage</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>第13关</t>
+          <t>第13关·分裂反弹</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Stage 13·Split &amp; Bounce</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>第14关</t>
+          <t>第14关·精英首现</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Stage 14·Elite Emerges</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>第15关</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>wheel</t>
-        </is>
-      </c>
+          <t>第15关·火焰筑墙</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>0</v>
       </c>
@@ -1262,10 +1321,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1274,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1286,216 +1345,241 @@
         <v>0</v>
       </c>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Stage 15·Wall of Flame</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>第16关</t>
+          <t>第16关·冲锋撕裂</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Stage 16·Cleave Rush</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>第17关</t>
+          <t>第17关·十字网</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Stage 17·Crossfire Net</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>第18关</t>
+          <t>第18关·元素混斗</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Stage 18·Elemental Melee</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>第19关</t>
+          <t>第19关·弹药耗尽</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Stage 19·Ammo Depleted</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>第20关</t>
+          <t>第20关·铁盾围城</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1504,10 +1588,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1522,17 +1606,562 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>centipede</t>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Stage 20·Iron Siege</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>第21关·全弹幕压制</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11</v>
+      </c>
+      <c r="O22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Stage 21·Full Barrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>第22关·冲锋撕裂 II</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>14</v>
+      </c>
+      <c r="J23" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" t="n">
+        <v>14</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Stage 22·Cleave II</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>第23关·精英汇聚</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" t="n">
+        <v>14</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>14</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Stage 23·Elite Convergence</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>第24关·火焰包围</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" t="n">
+        <v>14</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>15</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Stage 24·Ring of Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>第25关·反弹陷阱 II</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>15</v>
+      </c>
+      <c r="N26" t="n">
+        <v>15</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Stage 25·Ricochet II</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>第26关·分裂潮汐</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>16</v>
+      </c>
+      <c r="J27" t="n">
+        <v>16</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>15</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Stage 26·Splinter Tide</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>第27关·精英突袭</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>17</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>16</v>
+      </c>
+      <c r="N28" t="n">
+        <v>16</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Stage 27·Elite Raid</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>第28关·终章前哨</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>10</v>
+      </c>
+      <c r="K29" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" t="n">
+        <v>10</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Stage 28·Final Vanguard</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>29</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>第29关·弹幕地狱</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>12</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Stage 29·Bullet Hell</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>第30关·冲锋骑士</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>lancer_knight</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Stage 30·Lancer Knight</t>
         </is>
       </c>
     </row>

--- a/config/excel/stages.xlsx
+++ b/config/excel/stages.xlsx
@@ -423,14 +423,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
@@ -531,11 +531,6 @@
           <t>boss_id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>display_name_en</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -585,11 +580,6 @@
         <v>0</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Stage 1·Sortie</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -639,11 +629,6 @@
         <v>0</v>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Stage 2·Charge</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -693,11 +678,6 @@
         <v>0</v>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Stage 3·Longbow</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -747,11 +727,6 @@
         <v>0</v>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Stage 4·Shield Trial</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -801,11 +776,6 @@
         <v>0</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Stage 5·Splinter</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -855,11 +825,6 @@
         <v>0</v>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Stage 6·Buckshot</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -909,11 +874,6 @@
         <v>14</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Stage 7·Ricochet</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -963,11 +923,6 @@
         <v>0</v>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Stage 8·Cross Lock</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1017,11 +972,6 @@
         <v>0</v>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Stage 9·Pyromaster</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1075,11 +1025,6 @@
         <v>0</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Stage 10·Forge</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1129,11 +1074,6 @@
         <v>0</v>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Stage 11·Bash &amp; Break</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1156,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1168,26 +1108,21 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Stage 12·Barrage</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1207,7 +1142,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1219,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1234,14 +1169,9 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Stage 13·Split &amp; Bounce</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1261,10 +1191,10 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1291,11 +1221,6 @@
         <v>0</v>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Stage 14·Elite Emerges</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1321,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1333,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1345,11 +1270,6 @@
         <v>0</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Stage 15·Wall of Flame</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1399,11 +1319,6 @@
         <v>0</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Stage 16·Cleave Rush</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1453,11 +1368,6 @@
         <v>0</v>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Stage 17·Crossfire Net</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1507,11 +1417,6 @@
         <v>0</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Stage 18·Elemental Melee</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1561,11 +1466,6 @@
         <v>13</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Stage 19·Ammo Depleted</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1615,11 +1515,6 @@
         <v>0</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Stage 20·Iron Siege</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1669,11 +1564,6 @@
         <v>0</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Stage 21·Full Barrage</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1723,11 +1613,6 @@
         <v>0</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Stage 22·Cleave II</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1777,11 +1662,6 @@
         <v>0</v>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Stage 23·Elite Convergence</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1831,11 +1711,6 @@
         <v>0</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Stage 24·Ring of Fire</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1885,11 +1760,6 @@
         <v>15</v>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Stage 25·Ricochet II</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1939,11 +1809,6 @@
         <v>0</v>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Stage 26·Splinter Tide</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1993,11 +1858,6 @@
         <v>0</v>
       </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Stage 27·Elite Raid</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2047,11 +1907,6 @@
         <v>0</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Stage 28·Final Vanguard</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2101,11 +1956,6 @@
         <v>12</v>
       </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Stage 29·Bullet Hell</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2157,11 +2007,6 @@
       <c r="Q31" t="inlineStr">
         <is>
           <t>lancer_knight</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Stage 30·Lancer Knight</t>
         </is>
       </c>
     </row>

--- a/config/excel/stages.xlsx
+++ b/config/excel/stages.xlsx
@@ -628,7 +628,11 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>lancer_knight</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/config/excel/stages.xlsx
+++ b/config/excel/stages.xlsx
@@ -550,7 +550,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>

--- a/config/excel/stages.xlsx
+++ b/config/excel/stages.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="编码表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,26 +424,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,65 +478,110 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>display_name_en</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>room_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>reward_rooms</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>hp_coeff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>elite</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>berserker</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>splitter</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>archer</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>fire_mage</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>shotgun</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cross_shooter</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>bounce_slime</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>snake_shooter</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>jumper</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mini_centipede</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dasher</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>teleporter</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>boss_id</t>
         </is>
@@ -544,22 +599,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>第1关·出击</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>第1关</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -579,7 +634,34 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -593,22 +675,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>第2关·冲锋潮</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>第2关</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -623,16 +705,39 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>lancer_knight</t>
-        </is>
-      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -646,28 +751,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>第3关·长弓</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>第3关</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -676,12 +781,39 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -695,28 +827,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>第4关·铁盾试练</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>第4关</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stage 4</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -725,12 +861,39 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -744,25 +907,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>第5关·分裂噩梦</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>14</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
+          <t>第5关</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -779,7 +950,34 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -793,25 +991,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>第6关·霰弹阵</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>第6关</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Stage 6</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -820,15 +1018,42 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -842,28 +1067,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>第7关·反弹陷阱</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>第7关</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Stage 7</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>16</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -872,12 +1097,39 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -891,25 +1143,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>第8关·十字锁</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>第8关</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Stage 8</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -921,12 +1177,39 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -940,42 +1223,69 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>第9关·火焰宗师</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>第9关</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 9</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>15</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -989,23 +1299,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>第10关·打造</t>
+          <t>第10关</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>attr_forge</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
+          <t>Stage 10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1028,7 +1342,34 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1042,31 +1383,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>第11关·硬拆快攻</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>第11关</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Stage 11</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1075,9 +1416,36 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1091,42 +1459,69 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>第12关·弹幕包围</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>第12关</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Stage 12</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1140,42 +1535,69 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>第13关·分裂反弹</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>第13关</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Stage 13</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1189,28 +1611,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>第14关·精英首现</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>第14关</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Stage 14</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1224,7 +1646,34 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1238,19 +1687,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>第15关·火焰筑墙</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>第15关</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Stage 15</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1273,7 +1722,38 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>bounce_slime</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1287,42 +1767,69 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>第16关·冲锋撕裂</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>第16关</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Stage 16</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>13</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1336,42 +1843,69 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>第17关·十字网</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>第17关</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Stage 17</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1385,31 +1919,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>第18关·元素混斗</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>第18关</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Stage 18</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1420,7 +1958,34 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1434,19 +1999,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>第19关·弹药耗尽</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>第19关</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Stage 19</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1455,21 +2020,48 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>12</v>
       </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>12</v>
+      </c>
+      <c r="R20" t="n">
+        <v>12</v>
+      </c>
+      <c r="S20" t="n">
         <v>13</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1483,42 +2075,77 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>第20关·铁盾围城</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
+          <t>第20关</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Stage 20</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>10</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>15</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>13</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
         <v>13</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1532,42 +2159,69 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>第21关·全弹幕压制</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>第21关</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Stage 21</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>11</v>
       </c>
-      <c r="M22" t="n">
+      <c r="P22" t="n">
         <v>11</v>
       </c>
-      <c r="N22" t="n">
+      <c r="Q22" t="n">
         <v>11</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
         <v>10</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1581,42 +2235,69 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>第22关·冲锋撕裂 II</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>第22关</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Stage 22</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" t="n">
+      <c r="M23" t="n">
         <v>14</v>
       </c>
-      <c r="K23" t="n">
+      <c r="N23" t="n">
         <v>14</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>13</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1630,42 +2311,69 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>第23关·精英汇聚</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>第23关</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Stage 23</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>15</v>
-      </c>
-      <c r="I24" t="n">
-        <v>14</v>
-      </c>
-      <c r="J24" t="n">
-        <v>14</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1679,42 +2387,73 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>第24关·火焰包围</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>第24关</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Stage 24</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>15</v>
       </c>
-      <c r="I25" t="n">
+      <c r="L25" t="n">
         <v>14</v>
       </c>
-      <c r="J25" t="n">
+      <c r="M25" t="n">
         <v>14</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>15</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1728,31 +2467,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>第25关·反弹陷阱 II</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
+          <t>第25关</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Stage 25</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>15</v>
@@ -1763,7 +2510,34 @@
       <c r="P26" t="n">
         <v>15</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>15</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1777,42 +2551,69 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>第26关·分裂潮汐</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>第26关</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Stage 26</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>16</v>
       </c>
-      <c r="J27" t="n">
+      <c r="M27" t="n">
         <v>16</v>
       </c>
-      <c r="K27" t="n">
+      <c r="N27" t="n">
         <v>15</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
         <v>15</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1826,42 +2627,69 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>第27关·精英突袭</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>第27关</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Stage 27</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>15</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>17</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>16</v>
       </c>
-      <c r="N28" t="n">
+      <c r="Q28" t="n">
         <v>16</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1875,42 +2703,73 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>第28关·终章前哨</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>第28关</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Stage 28</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" t="n">
-        <v>16</v>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>10</v>
       </c>
       <c r="K29" t="n">
+        <v>16</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>10</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>10</v>
       </c>
       <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>10</v>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1924,19 +2783,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>第29关·弹幕地狱</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>第29关</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Stage 29</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1945,13 +2804,13 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>12</v>
@@ -1959,7 +2818,34 @@
       <c r="P30" t="n">
         <v>12</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>12</v>
+      </c>
+      <c r="S30" t="n">
+        <v>12</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1973,19 +2859,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>第30关·冲锋骑士</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>第30关</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Stage 30</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2008,9 +2894,740 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>dark_dragon</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>可填值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>中文名</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(空)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>普通战斗</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>默认值，普通战斗关</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>attr_forge</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>属性打造关</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>进入打造房（无需天赋卡解锁）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>奖励房</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>走 reward_rooms 抽房</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>reward_rooms</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>转盘</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>当前唯一实现的奖励房类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(空)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>普通关</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>无主题</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>demon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>恶魔关</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>通关弹恶魔主题奖励卡（接受/放弃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>angel</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天使关</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>通关弹天使主题奖励卡（接受/放弃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>恶魔/天使随机</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>本关随机分配恶魔或天使主题，本局内固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>boss_id</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(空)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>无 boss</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>普通战斗关</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>boss_id</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>centipede</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>千足虫</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>boss_id</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>lancer_knight</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>冲锋骑士</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>boss_id</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dark_dragon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>暗黑龙</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>boss_id</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bounce_slime</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>弹射史莱姆</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>boss_id</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>laser_snail</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>激光蜗牛</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>小怪列 normal</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>普通怪</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>小怪列 elite</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>高级怪</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>小怪列 shield</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SHIELD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>盾牌怪</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>小怪列 berserker</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BERSERKER</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>狂战士</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>小怪列 splitter</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SPLITTER</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>分裂怪</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>小怪列 archer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ARCHER</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>射箭怪</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>小怪列 fire_mage</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FIRE_MAGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>火焰法师</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>小怪列 shotgun</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SHOTGUN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>霰弹怪</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>小怪列 cross_shooter</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CROSS_SHOOTER</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>十字子弹怪</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>小怪列 bounce_slime</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BOUNCE_SLIME</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>反弹子弹怪</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>小怪列 snake_shooter</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SNAKE_SHOOTER</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>蛇形子弹怪</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>小怪列 jumper</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JUMPER</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>跳跃怪</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>小怪列 laser</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LASER</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>激光怪</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>小怪列 mini_centipede</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MINI_CENTIPEDE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>迷你千足虫</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>小怪列 dasher</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DASHER</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>冲刺怪</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>小怪列 teleporter</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TELEPORTER</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>瞬移怪</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>填该关此种怪物的生成数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>hp_coeff</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.0 / 1.05 / ...</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>每关 HP 系数</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>累积乘积：第N关 HP = base × ∏(coeff[0..N])，取代旧 pow(stage_hp_growth) 指数曲线</t>
         </is>
       </c>
     </row>
